--- a/data/trans_orig/P36BPD07_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023</t>
+          <t>Población según el número de bebidas carbonatadas y/o azucaradas que consume al día en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>137980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188864</t>
+          <t>187719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114312</t>
+          <t>114260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148522</t>
+          <t>149358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264244</t>
+          <t>262575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322685</t>
+          <t>320223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444629</t>
+          <t>445774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494046</t>
+          <t>495513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>526276</t>
+          <t>525440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560486</t>
+          <t>560538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>985606</t>
+          <t>988068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1044047</t>
+          <t>1045716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,93%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160172</t>
+          <t>144900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>405512</t>
+          <t>403637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>238330</t>
+          <t>237569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286854</t>
+          <t>286231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>393216</t>
+          <t>389260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>656028</t>
+          <t>657056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>786515</t>
+          <t>788390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1031855</t>
+          <t>1047127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>670929</t>
+          <t>671552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>719453</t>
+          <t>720214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1493782</t>
+          <t>1492754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1756594</t>
+          <t>1760550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144852</t>
+          <t>144499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198736</t>
+          <t>196664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79256</t>
+          <t>72464</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199206</t>
+          <t>197978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214345</t>
+          <t>211164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372594</t>
+          <t>373790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505944</t>
+          <t>508016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>559828</t>
+          <t>560181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>734160</t>
+          <t>735388</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>854110</t>
+          <t>860902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1265452</t>
+          <t>1264256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1423701</t>
+          <t>1426882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233882</t>
+          <t>229870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294038</t>
+          <t>293075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183926</t>
+          <t>188652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259939</t>
+          <t>262071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>435524</t>
+          <t>437005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>542645</t>
+          <t>538708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>630737</t>
+          <t>631700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>690893</t>
+          <t>694905</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>830409</t>
+          <t>828277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>906422</t>
+          <t>901696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1472479</t>
+          <t>1476416</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1579600</t>
+          <t>1578119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>709792</t>
+          <t>698607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>995730</t>
+          <t>992630</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>630700</t>
+          <t>636025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>837814</t>
+          <t>843235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1672793</t>
+          <t>1672794</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1444774</t>
+          <t>1456891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1804471</t>
+          <t>1803512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2459246</t>
+          <t>2462346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2745184</t>
+          <t>2756369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2818481</t>
+          <t>2813060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3025595</t>
+          <t>3020270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5306799</t>
+          <t>5307759</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5666496</t>
+          <t>5654380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111270</t>
+          <t>7111271</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD07_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>160940</t>
+          <t>172508</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137980</t>
+          <t>148692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187719</t>
+          <t>197722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>130450</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114260</t>
+          <t>127091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149358</t>
+          <t>167550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>291391</t>
+          <t>318022</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>262575</t>
+          <t>289572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>320223</t>
+          <t>351072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>472553</t>
+          <t>516047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445774</t>
+          <t>490833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495513</t>
+          <t>539863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>544348</t>
+          <t>586541</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>525440</t>
+          <t>564505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560538</t>
+          <t>604964</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1016900</t>
+          <t>1102588</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>988068</t>
+          <t>1069538</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1045716</t>
+          <t>1131038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633493</t>
+          <t>688555</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633493</t>
+          <t>688555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633493</t>
+          <t>688555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674798</t>
+          <t>732055</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674798</t>
+          <t>732055</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674798</t>
+          <t>732055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1308291</t>
+          <t>1420610</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1308291</t>
+          <t>1420610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1308291</t>
+          <t>1420610</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>309830</t>
+          <t>343709</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>144900</t>
+          <t>305665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>403637</t>
+          <t>379681</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>260897</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>237569</t>
+          <t>272881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286231</t>
+          <t>326387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>570728</t>
+          <t>642785</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>389260</t>
+          <t>598054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>657056</t>
+          <t>686350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>882197</t>
+          <t>704343</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>788390</t>
+          <t>668371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1047127</t>
+          <t>742387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>696886</t>
+          <t>770271</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>671552</t>
+          <t>742960</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>720214</t>
+          <t>796466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1579082</t>
+          <t>1474615</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1492754</t>
+          <t>1431050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1760550</t>
+          <t>1519346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957783</t>
+          <t>1069347</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957783</t>
+          <t>1069347</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957783</t>
+          <t>1069347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149810</t>
+          <t>2117400</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149810</t>
+          <t>2117400</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149810</t>
+          <t>2117400</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>169851</t>
+          <t>193221</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144499</t>
+          <t>164702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196664</t>
+          <t>225481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>146645</t>
+          <t>173032</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72464</t>
+          <t>151337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197978</t>
+          <t>195007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>316496</t>
+          <t>366253</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>211164</t>
+          <t>330966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373790</t>
+          <t>402533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>534829</t>
+          <t>609852</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508016</t>
+          <t>577592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560181</t>
+          <t>638371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>786721</t>
+          <t>639227</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>735388</t>
+          <t>617252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>860902</t>
+          <t>660922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1321550</t>
+          <t>1249079</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1264256</t>
+          <t>1212799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1426882</t>
+          <t>1284366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>262177</t>
+          <t>297165</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>229870</t>
+          <t>266097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>293075</t>
+          <t>329461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>232002</t>
+          <t>265936</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188652</t>
+          <t>241180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262071</t>
+          <t>294842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>494179</t>
+          <t>563101</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>437005</t>
+          <t>518288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>538708</t>
+          <t>604312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>662598</t>
+          <t>690762</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631700</t>
+          <t>658466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>694905</t>
+          <t>721830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>858346</t>
+          <t>848381</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>828277</t>
+          <t>819475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>901696</t>
+          <t>873137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1520945</t>
+          <t>1539142</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1476416</t>
+          <t>1497931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1578119</t>
+          <t>1583955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924775</t>
+          <t>987927</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924775</t>
+          <t>987927</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924775</t>
+          <t>987927</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090348</t>
+          <t>1114317</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090348</t>
+          <t>1114317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090348</t>
+          <t>1114317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2015124</t>
+          <t>2102243</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2015124</t>
+          <t>2102243</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2015124</t>
+          <t>2102243</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>902799</t>
+          <t>1006603</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>698607</t>
+          <t>943775</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>1067488</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>769995</t>
+          <t>883558</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>636025</t>
+          <t>833195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>843235</t>
+          <t>933759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1672794</t>
+          <t>1890161</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1456891</t>
+          <t>1808856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1803512</t>
+          <t>1967680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2462346</t>
+          <t>2460119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2756369</t>
+          <t>2583832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2813060</t>
+          <t>2794219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3020270</t>
+          <t>2894783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5307759</t>
+          <t>5287905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5654380</t>
+          <t>5446729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
